--- a/know-all/outputs/20260323_红酒/01_审核稿.xlsx
+++ b/know-all/outputs/20260323_红酒/01_审核稿.xlsx
@@ -39,6 +39,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00222222"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -72,20 +73,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,13 +456,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -471,45 +471,40 @@
           <t>专题信息</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>专题</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>红酒</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>专题</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>红酒</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>待人工确认</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>这份本地表格是当前审核阶段唯一 source of truth。</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>本地审核表格是审核阶段唯一 source of truth。只有在用户明确确认后，才允许进入出图。</t>
         </is>
       </c>
     </row>
@@ -520,7 +515,7 @@
           <t>标题</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>红酒这5件事别想当然🍷</t>
         </is>
@@ -535,24 +530,24 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>主标题</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>很多人喝红酒，但没真搞懂红酒</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>副标题</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>从颜色到醒酒，这几件事最容易想当然</t>
         </is>
@@ -560,454 +555,448 @@
     </row>
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>封面列点</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>mark_raw</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>mark_render</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>🍇</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>红</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>红酒颜色不是果肉给的</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>🍷</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>挂</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>挂杯不等于酒更好</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>醒</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>醒酒不是越久越好</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>📅</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>红</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>红酒也不是越老越值钱</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="78" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>🔩</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>螺</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>螺旋盖不等于便宜酒</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="78" customHeight="1"/>
-    <row r="20" ht="78" customHeight="1">
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>知识卡</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>卡片ID</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>mark_raw</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>mark_render</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>正文1</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>正文2</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>正文3</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>正文4</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="92" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>颜色不是果肉给的 🍇</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>🍇</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>葡</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>很多人一看到红酒是红的，就会很自然地觉得：那肯定是因为葡萄里面本来就是红色的汁。这个想法特别顺，因为“红葡萄酿红酒”听上去就像颜色会直接从果肉里流出来，很多人第一次接触红酒时，几乎都会这么理解。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>但大多数酿红酒的葡萄，挤出来的汁其实没有你想得那么红。红酒真正的颜色，主要来自葡萄皮。发酵时如果让果皮和葡萄汁一起待上一段时间，颜色、单宁和一部分风味就会慢慢被带出来，所以最后酒液才会变深。浸皮时间越长，通常颜色也会更深，口感也会更有抓力。</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>也就是说，红酒之所以是红酒，关键不只是“用了红葡萄”，更重要的是酿的时候有没有让皮和汁一起发酵。很多人以为颜色是果肉天生带的，其实决定性更强的是工艺。</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>挂杯不等于酒更好 🍷</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>🍷</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>杯</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>很多人一晃酒杯，看到杯壁上慢慢往下流的“酒腿”，就会下意识觉得：这酒不错，挂杯这么明显。这个判断会流行，是因为挂杯特别直观，肉眼一下就能看到，天然容易被当成“高级感”的证据。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>但挂杯这件事，和“是不是好酒”并没有那么直接。它更多和酒精、糖分、甘油这些因素有关。酒精度高一点，或者残糖多一点，挂杯往往就更明显。所以你看到它“挂得漂亮”，不等于它在风味层次、平衡感、复杂度上就一定更强。它只能说明酒液的物理表现是这样，不能代替真正的品尝。</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>红酒好不好，最后还是要回到闻起来香不香、喝起来酸度和单宁平不平衡、收尾干不干净。挂杯可以看，但它更像一个附带信号，不是整杯酒质量的总判决。</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="78" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="92" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>醒酒不是越久越好 ⏳</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>⏳</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>醒</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>一说到红酒，很多人就会自动把“醒酒”理解成一个固定动作，仿佛越高级的酒，就越该多醒一会儿。于是有些人一开瓶先放上一两个小时，觉得这样才算讲究，好像时间给得越久，酒就一定会越开、越好喝。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>但醒酒的作用，本质上是让酒和空气接触，帮助一些比较闷的香气慢慢打开，也让某些年轻、收得比较紧的酒喝起来没那么硬。可如果酒本身就比较轻、比较老，或者香气已经很脆弱，醒太久反而容易把它醒散了，果香掉得快，整体会变空。不是所有红酒都需要被“打开”得那么彻底。</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>所以醒酒更像“看状态处理”，不是机械照做。年轻、封闭、结构重一点的酒可以多给一点时间；轻盈型或者老年份酒，很多时候反而应该边喝边观察，而不是一上来就长时间暴露在空气里。</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="92" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>红酒也不是越老越值钱 📅</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>📅</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>很多人一看到红酒瓶上的年份，就会很自然地觉得：年份越久，这酒应该就越厉害。这个印象很容易成立，因为“老酒更贵”在很多消费场景里本来就很常见，所以大家很容易把这种判断直接套到所有红酒身上。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>但红酒真不是都适合久放。大部分日常消费型红酒，本来就是为了在相对年轻的时候喝掉，讲究的是果味新鲜、结构顺口，不是靠十几年陈年去慢慢熬出来。如果把这类酒放太久，它最先掉下去的往往就是原本最讨喜的果香，最后剩下“放了很久”，不一定剩下“更好喝”。</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>真正适合陈年的，通常得有比较好的酸度、单宁、酒精和整体平衡感，能撑得住时间慢慢改它。所以红酒能不能久放，关键不是“是不是红酒”，而是这瓶酒本身有没有那个底子。年份可以参考，但不能单独拿来代替品质判断。</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="92" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>螺旋盖不等于便宜酒 🔩</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>🔩</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>盖</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>很多人看到螺旋盖，第一反应还是会觉得：这酒是不是不太行，连木塞都没有。因为在很多人的印象里，木塞更“传统”，也更像高档红酒该有的样子，所以螺旋盖很容易被自动归进“便宜”“随便喝喝”的那一档。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>但这几年这个印象已经越来越站不住了。螺旋盖最大的好处，是稳定。它能减少木塞污染，也更方便控制密封状态。尤其是一些主打新鲜果香、希望尽快饮用的酒，螺旋盖反而很合适，因为酒厂更在意的是把风味稳稳保住，而不是额外制造一种“传统高级感”。对日常饮用型红酒来说，它常常是实用选择，不是廉价替代。</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>所以“木塞更高级、螺旋盖更低端”很多时候是包装认知，不完全是酒本身的质量差异。你看到的是瓶口形式，酒厂真正考虑的往往是风格、稳定性和适饮期。</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="78" customHeight="1"/>
-    <row r="28" ht="78" customHeight="1"/>
-    <row r="29" ht="78" customHeight="1"/>
-    <row r="30" ht="78" customHeight="1">
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="92" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1"/>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>#话题</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="78" customHeight="1">
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>话题</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="78" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
           <t>#红酒知识</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="78" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>#葡萄酒入门</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="78" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>#喝酒日常</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="78" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>#生活常识</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="78" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>#涨知识</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="78" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>#每日闲聊语料库</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="78" customHeight="1"/>
-    <row r="39" ht="78" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1"/>
+    <row r="38" ht="24" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1"/>
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>确认说明</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>请直接修改这份本地表格。只有在明确说“文稿无误”或“可以出图”后，才允许进入出图阶段。</t>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>请直接修改这份本地审核表格。只有在明确说“文稿无误”或“可以出图”后，才允许进入图片阶段。</t>
         </is>
       </c>
     </row>
